--- a/stories/arbres/ATOM-TMP.MOI.001-01.xlsx
+++ b/stories/arbres/ATOM-TMP.MOI.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sara ouvre un grand calendrier avec maman. Maman lit les douze mois. Janvier, février, mars, avril. Mai, juin, juillet, août. Septembre, octobre, novembre, décembre. Sara pose son doigt. Maman dit : en juin, c'est ton anniversaire. Sara sourit. Elle aura un gâteau. Papa arrivera avec des fleurs. Maman répète : il y a douze mois. Un anniversaire a un mois. Le mois de Sara, c'est juin.</t>
+          <t>Sara ouvre un grand calendrier avec maman. Maman lit les douze mois. Janvier, février, mars, avril. Mai, juin, juillet, août. Septembre, octobre, novembre, décembre. Sara pose son doigt. En juin, c'est ton anniversaire. Sara sourit. Elle aura un gâteau. Papa arrivera avec des fleurs. Maman répète : il y a douze mois. Un anniversaire a un mois. Le mois de Sara, c'est juin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sara ouvre un grand calendrier avec maman. Maman lit les douze mois. Janvier, février, mars, avril. Mai, juin, juillet, août. Septembre, octobre, novembre, décembre. Sara pose son doigt.
+maman|En juin, c'est ton anniversaire.
+narrateur|Sara sourit. Elle aura un gâteau. Papa arrivera avec des fleurs. Maman répète : il y a douze mois. Un anniversaire a un mois. Le mois de Sara, c'est juin.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a un gâteau en juin. Pourquoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a entendu les douze mois. Son anniversaire est en juin. Maman était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1824,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sara ferme le calendrier. Elle range le crayon.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1991,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.MOI.001-01.xlsx
+++ b/stories/arbres/ATOM-TMP.MOI.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Sara sourit. Elle aura un gâteau. Papa arrivera avec des fleurs. Maman répète : il y a douze mois. Un anniversaire a un mois. Le mois de Sara, c'est juin.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Sara a un gâteau en juin. Pourquoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Sara a entendu les douze mois. Son anniversaire est en juin. Maman était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1837,7 @@
           <t>narrateur|Sara ferme le calendrier. Elle range le crayon.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2048,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2263,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.MOI.001-01.xlsx
+++ b/stories/arbres/ATOM-TMP.MOI.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L'anniversaire de Sara en juin</t>
+          <t>La fraise trop verte</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>C'est l'anniversaire de Sarah, en juin, quand les fraises du jardin sont mûres. Elle en cueille une trop verte. La rouge est bonne. Le gâteau attend, parfumé.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sara ouvre un grand calendrier avec maman. Maman lit les douze mois. Janvier, février, mars, avril. Mai, juin, juillet, août. Septembre, octobre, novembre, décembre. Sara pose son doigt. En juin, c'est ton anniversaire. Sara sourit. Elle aura un gâteau. Papa arrivera avec des fleurs. Maman répète : il y a douze mois. Un anniversaire a un mois. Le mois de Sara, c'est juin.</t>
+          <t>Sous les feuilles, une fraise cache sa joue rouge. Le jardin sent le sucre et la terre chaude. Une abeille passe loin, très loin. C'est juin, Sarah. Les fraises sont prêtes. C'est mon mois. Oui. Ton anniversaire. Le petit panier de paille attend près du pied. Sarah s'accroupit. Une feuille lui chatouille le poignet. J en vois une. Tu la prends ? Sarah tire. La fraise vient, trop claire. Elle est presque blanche, un peu dure. Elle est petite. Elle est trop verte. Elle n'est pas prête. Sarah la pose dans l'herbe. La fraise verte reste au pied. Je la laisse. Oui. On cherche une rouge. En ce moment, Sarah lève une feuille. Une fraise sombre brille dessous. Celle-là. Elle est mûre. Sarah la cueille, tout doux. Le fruit est chaud de soleil. Tu la sens ? Ça sent le gâteau. On en mettra dessus. Le panier reçoit trois rouges. Puis une quatrième, un peu plus petite. Juin donne les fraises. Et toi, tu as un an de plus.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sara ouvre un grand calendrier avec maman. Maman lit les &lt;emphasis level="moderate"&gt;douze&lt;/emphasis&gt; mois. Janvier, février, mars, avril. Mai, juin, juillet, août. Septembre, octobre, novembre, décembre. Sara pose son doigt. Maman dit : en juin, c'est ton anniversaire. Sara sourit. Elle aura un gâteau. Papa arrivera avec des fleurs. Maman répète : il y a douze mois. Un anniversaire a un mois. Le mois de Sara, c'est juin.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sous les feuilles, une fraise cache sa joue rouge. Le jardin sent le sucre et la terre chaude. Une abeille passe loin, très loin. C'est juin, Sarah. Les fraises sont prêtes. C'est mon mois. Oui. Ton anniversaire. Le petit panier de paille attend près du pied. Sarah s'accroupit. Une feuille lui chatouille le poignet. J en vois une. Tu la prends ? Sarah tire. La fraise vient, trop claire. Elle est presque blanche, un peu dure. Elle est petite. Elle est trop verte. Elle n'est pas prête. Sarah la pose dans l'herbe. La fraise verte reste au pied. Je la laisse. Oui. On cherche une rouge. En ce moment, Sarah lève une feuille. Une fraise sombre brille dessous. Celle-là. Elle est mûre. Sarah la cueille, tout doux. Le fruit est chaud de soleil. Tu la sens ? Ça sent le gâteau. On en mettra dessus. Le panier reçoit trois rouges. Puis une quatrième, un peu plus petite. Juin donne les fraises. Et toi, tu as un an de plus.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,12 +1324,45 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Sara ouvre un grand calendrier avec maman. Maman lit les douze mois. Janvier, février, mars, avril. Mai, juin, juillet, août. Septembre, octobre, novembre, décembre. Sara pose son doigt.
-maman|En juin, c'est ton anniversaire.
-narrateur|Sara sourit. Elle aura un gâteau. Papa arrivera avec des fleurs. Maman répète : il y a douze mois. Un anniversaire a un mois. Le mois de Sara, c'est juin.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Sous les feuilles, une fraise cache sa joue rouge.
+narrateur|Le jardin sent le sucre et la terre chaude.
+narrateur|Une abeille passe loin, très loin.
+maman|C'est juin, Sarah.
+maman|Les fraises sont prêtes.
+enfant-f|C'est mon mois.
+maman|Oui.
+maman|Ton anniversaire.
+narrateur|Le petit panier de paille attend près du pied.
+narrateur|Sarah s'accroupit.
+narrateur|Une feuille lui chatouille le poignet.
+enfant-f|J en vois une.
+maman|Tu la prends ?
+narrateur|Sarah tire.
+narrateur|La fraise vient, trop claire.
+narrateur|Elle est presque blanche, un peu dure.
+enfant-f|Elle est petite.
+maman|Elle est trop verte.
+maman|Elle n'est pas prête.
+narrateur|Sarah la pose dans l'herbe.
+narrateur|La fraise verte reste au pied.
+enfant-f|Je la laisse.
+maman|Oui.
+maman|On cherche une rouge.
+narrateur|En ce moment, Sarah lève une feuille.
+narrateur|Une fraise sombre brille dessous.
+enfant-f|Celle-là.
+maman|Elle est mûre.
+narrateur|Sarah la cueille, tout doux.
+narrateur|Le fruit est chaud de soleil.
+maman|Tu la sens ?
+enfant-f|Ça sent le gâteau.
+maman|On en mettra dessus.
+narrateur|Le panier reçoit trois rouges.
+narrateur|Puis une quatrième, un peu plus petite.
+maman|Juin donne les fraises.
+maman|Et toi, tu as un an de plus.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,12 +1387,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Sara a un gâteau en juin. Pourquoi ?</t>
+          <t>Sarah a un gâteau en juin. Pourquoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sara a un gâteau en juin. Pourquoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a un gâteau en juin. Pourquoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1362,7 +1407,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>anniversaire | son anniversaire | juin | le mois</t>
+          <t>anniversaire | son anniversaire | juin | le mois | fraises</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1426,7 +1471,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1498,10 +1543,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Sara a un gâteau en juin. Pourquoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Sarah a un gâteau en juin.
+narrateur|Pourquoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1526,12 +1571,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sara a entendu les douze mois. Son anniversaire est en juin. Maman était là.</t>
+          <t>Elles rentrent. La cuisine sent déjà la pâte chaude. Le gâteau repose, tout nu. Il attend les fraises. Oui. Parce que c'est ton anniversaire. Sarah pose une rouge au milieu. Le jus tache un peu le dessus. Une étoile. Une fraise. Elle en pose deux autres, tout autour. La verte reste au jardin. Elle grandira. En juin, les rouges d'abord. Maman coupe une part mince. Sarah tient l'assiette à deux mains. Tu goûtes ?</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sara a entendu les &lt;emphasis level="moderate"&gt;douze&lt;/emphasis&gt; mois. Son anniversaire est en juin. Maman était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Elles rentrent. La cuisine sent déjà la pâte chaude. Le gâteau repose, tout nu. Il attend les fraises. Oui. Parce que c'est ton anniversaire. Sarah pose une rouge au milieu. Le jus tache un peu le dessus. Une étoile. Une fraise. Elle en pose deux autres, tout autour. La verte reste au jardin. Elle grandira. En juin, les rouges d'abord. Maman coupe une part mince. Sarah tient l'assiette à deux mains. Tu goûtes ?</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1594,7 +1639,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1670,10 +1715,25 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sara a entendu les douze mois. Son anniversaire est en juin. Maman était là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Elles rentrent.
+narrateur|La cuisine sent déjà la pâte chaude.
+narrateur|Le gâteau repose, tout nu.
+enfant-f|Il attend les fraises.
+maman|Oui.
+maman|Parce que c'est ton anniversaire.
+narrateur|Sarah pose une rouge au milieu.
+narrateur|Le jus tache un peu le dessus.
+enfant-f|Une étoile.
+maman|Une fraise.
+narrateur|Elle en pose deux autres, tout autour.
+maman|La verte reste au jardin.
+enfant-f|Elle grandira.
+maman|En juin, les rouges d'abord.
+narrateur|Maman coupe une part mince.
+narrateur|Sarah tient l'assiette à deux mains.
+maman|Tu goûtes ?</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1698,12 +1758,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sara ferme le calendrier. Elle range le crayon.</t>
+          <t>Sarah croque la fraise du dessus. Le jus sucré lui reste au menton. Elle est bonne. Parce qu elle était rouge. Une graine minuscule colle au doigt. Sarah la souffle. Merci, Sarah. Tu as choisi les mûres. Pas la verte. Pas la verte. Le panier a encore deux fruits. Ils sentent le soleil de juin. C'est mon mois. Le mois de ton anniversaire. Une mouche tourne près de la fenêtre. On range le reste au frais.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sara ferme le calendrier. Elle range le crayon.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah croque la fraise du dessus. Le jus sucré lui reste au menton. Elle est bonne. Parce qu elle était rouge. Une graine minuscule colle au doigt. Sarah la souffle. Merci, Sarah. Tu as choisi les mûres. Pas la verte. Pas la verte. Le panier a encore deux fruits. Ils sentent le soleil de juin. C'est mon mois. Le mois de ton anniversaire. Une mouche tourne près de la fenêtre. On range le reste au frais.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1766,7 +1826,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1834,10 +1894,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sara ferme le calendrier. Elle range le crayon.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Sarah croque la fraise du dessus.
+narrateur|Le jus sucré lui reste au menton.
+enfant-f|Elle est bonne.
+maman|Parce qu elle était rouge.
+narrateur|Une graine minuscule colle au doigt.
+narrateur|Sarah la souffle.
+maman|Merci, Sarah.
+maman|Tu as choisi les mûres.
+enfant-f|Pas la verte.
+maman|Pas la verte.
+narrateur|Le panier a encore deux fruits.
+narrateur|Ils sentent le soleil de juin.
+enfant-f|C'est mon mois.
+maman|Le mois de ton anniversaire.
+narrateur|Une mouche tourne près de la fenêtre.
+maman|On range le reste au frais.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1862,12 +1936,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah essuie le menton d'un revers. Il reste une trace rose. Encore un peu de jus. C'est le goût de juin. Le gâteau a un trou au milieu. Là où la fraise était. Elle est dans mon ventre. Oui. Dehors, la verte attend sous sa feuille. Dedans, le panier sent encore le jardin.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah essuie le menton d'un revers. Il reste une trace rose. Encore un peu de jus. C'est le goût de juin. Le gâteau a un trou au milieu. Là où la fraise était. Elle est dans mon ventre. Oui. Dehors, la verte attend sous sa feuille. Dedans, le panier sent encore le jardin.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1923,14 +1997,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2002,10 +2076,18 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Sarah essuie le menton d'un revers.
+narrateur|Il reste une trace rose.
+enfant-f|Encore un peu de jus.
+maman|C'est le goût de juin.
+narrateur|Le gâteau a un trou au milieu.
+narrateur|Là où la fraise était.
+enfant-f|Elle est dans mon ventre.
+maman|Oui.
+narrateur|Dehors, la verte attend sous sa feuille.
+narrateur|Dedans, le panier sent encore le jardin.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2062,6 +2144,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.MOI.001-01.xlsx
+++ b/stories/arbres/ATOM-TMP.MOI.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maison</t>
+          <t>jardin de fraisiers, puis table de la cuisine</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sara, maman</t>
+          <t>Sarah, maman</t>
         </is>
       </c>
     </row>
